--- a/qwen3-asr-local/benchmark_results/final_benchmark_sheet.xlsx
+++ b/qwen3-asr-local/benchmark_results/final_benchmark_sheet.xlsx
@@ -33,7 +33,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -43,6 +43,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="002C3E50"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F9F9F9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
   </fills>
@@ -72,13 +82,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -446,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O5"/>
+  <dimension ref="A1:O60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -469,24 +485,24 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ASR Model:</t>
+          <t>ASR Models:</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Qwen3-ASR-1.7B-Q8_0</t>
+          <t>Qwen3-ASR-1.7B-BF16-new, Qwen3-ASR-1.7B-Q8_0-new</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Translation Model:</t>
+          <t>Translation Models:</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Qwen3-8B-Q5_K_M</t>
+          <t>Qwen3-4B-BF16, Qwen3-4B-Q4_K_M, Qwen3-4B-Q8_0, Qwen3-8B-BF16, Qwen3-8B-Q4_K_M, Qwen3-8B-Q5_K_M, Qwen3-8B-Q8_0</t>
         </is>
       </c>
     </row>
@@ -570,7 +586,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Qwen3-ASR-1.7B-Q8_0</t>
+          <t>Qwen3-ASR-1.7B-Q8_0-new</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -585,37 +601,37 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>9.02</t>
+          <t>5.20</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>18.00</t>
+          <t>16</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>32.00</t>
+          <t>35</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>50.00</t>
+          <t>51</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>332.45</t>
+          <t>588.46</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>8.22</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
@@ -630,17 +646,4252 @@
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t>Hello. This is a test of the Quenae's speech recognition system. The quick brown fox jumps over the lazy dog.</t>
+          <t>Hello. This is a test of the speech recognition system. The quick brown fox jumps over the lazy dog.</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t>Hello. This is a test of the Quenae's speech recognition system. The quick brown fox jumps over the lazy dog.</t>
+          <t>Hello. This is a test of the speech recognition system. The quick brown fox jumps over the lazy dog.</t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>ہیلو۔ یہ کوئنے کی بول ڈیٹا تشخیص نظام کا ایک ٹیسٹ ہے۔ تیز سیاہ گھوڑا معمور کرکے لاتا ہے۔</t>
+          <t>ہیلو۔ یہ اسپیچ ریکگنیشن سسٹم کا ایک ٹیسٹ ہے۔ تیز بھوری لومڑی سست کتے کے اوپر سے کودتی ہے۔</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Qwen3-ASR-1.7B-Q8_0-new</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Qwen3-8B-Q5_K_M</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>sample_en2.wav</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>4.80</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>675.0</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>2.48</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>8.22</t>
+        </is>
+      </c>
+      <c r="K6" s="4" t="inlineStr">
+        <is>
+          <t>N/A (CPU-only, Metal OFF)</t>
+        </is>
+      </c>
+      <c r="L6" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M6" s="4" t="inlineStr">
+        <is>
+          <t>Good morning. How are you doing today? I hope everything is going well.</t>
+        </is>
+      </c>
+      <c r="N6" s="4" t="inlineStr">
+        <is>
+          <t>Good morning. How are you doing today? I hope everything is going well.</t>
+        </is>
+      </c>
+      <c r="O6" s="4" t="inlineStr">
+        <is>
+          <t>صبح بخیر۔ آج آپ کیسے ہیں؟ مجھے امید ہے کہ سب کچھ ٹھیک چل رہا ہے۔</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Qwen3-ASR-1.7B-Q8_0-new</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Qwen3-8B-Q5_K_M</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>sample_ur1.wav</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>775.61</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>2.48</t>
+        </is>
+      </c>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>8.22</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="inlineStr">
+        <is>
+          <t>N/A (CPU-only, Metal OFF)</t>
+        </is>
+      </c>
+      <c r="L7" s="5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M7" s="5" t="inlineStr">
+        <is>
+          <t>aaj ka mausam bohat acha hai aur dhoop bhi nikal rahi hai</t>
+        </is>
+      </c>
+      <c r="N7" s="5" t="inlineStr">
+        <is>
+          <t>Today the weather is very nice and the sun is also shining.</t>
+        </is>
+      </c>
+      <c r="O7" s="5" t="inlineStr">
+        <is>
+          <t>آج کا موسم بہت اچھا ہے اور دھوپ بھی نکل رہی ہے۔</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Qwen3-ASR-1.7B-Q8_0-new</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Qwen3-8B-Q5_K_M</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>sample_ur2.wav</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>861.54</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>2.48</t>
+        </is>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>8.22</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="inlineStr">
+        <is>
+          <t>N/A (CPU-only, Metal OFF)</t>
+        </is>
+      </c>
+      <c r="L8" s="5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M8" s="5" t="inlineStr">
+        <is>
+          <t>main aap se milna chahta hoon agr aap ke paas waqt ho to</t>
+        </is>
+      </c>
+      <c r="N8" s="5" t="inlineStr">
+        <is>
+          <t>I would like to meet you if you have time.</t>
+        </is>
+      </c>
+      <c r="O8" s="5" t="inlineStr">
+        <is>
+          <t>میں آپ سے ملنا چاہتا ہوں اگر آپ کے پاس وقت ہو تو۔</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Qwen3-ASR-1.7B-Q8_0-new</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Qwen3-8B-Q8_0</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>sample_en1.wav</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>5.20</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>819.23</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>2.48</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>11.95</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>N/A (CPU-only, Metal OFF)</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>Hello. This is a test of the speech recognition system. The quick brown fox jumps over the lazy dog.</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t>Hello. This is a test of the speech recognition system. The quick brown fox jumps over the lazy dog.</t>
+        </is>
+      </c>
+      <c r="O9" s="3" t="inlineStr">
+        <is>
+          <t>ہیلو۔ یہ اسپیچ ریکگنیشن سسٹم کا ایک ٹیسٹ ہے۔ تیز بھوری لومڑی سست کتے کے اوپر سے کودتی ہے۔</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Qwen3-ASR-1.7B-Q8_0-new</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Qwen3-8B-Q8_0</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>sample_en2.wav</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>4.80</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>925.0</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>2.48</t>
+        </is>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>11.95</t>
+        </is>
+      </c>
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t>N/A (CPU-only, Metal OFF)</t>
+        </is>
+      </c>
+      <c r="L10" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M10" s="4" t="inlineStr">
+        <is>
+          <t>Good morning. How are you doing today? I hope everything is going well.</t>
+        </is>
+      </c>
+      <c r="N10" s="4" t="inlineStr">
+        <is>
+          <t>Good morning. How are you doing today? I hope everything is going well.</t>
+        </is>
+      </c>
+      <c r="O10" s="4" t="inlineStr">
+        <is>
+          <t>صبح بخیر۔ آج آپ کیسے ہیں؟ مجھے امید ہے کہ سب کچھ ٹھیک چل رہا ہے۔</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Qwen3-ASR-1.7B-Q8_0-new</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Qwen3-8B-Q8_0</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>sample_ur1.wav</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>980.49</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>2.48</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>11.95</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="inlineStr">
+        <is>
+          <t>N/A (CPU-only, Metal OFF)</t>
+        </is>
+      </c>
+      <c r="L11" s="5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M11" s="5" t="inlineStr">
+        <is>
+          <t>aaj ka mausam bohat acha hai aur dhoop bhi nikal rahi hai</t>
+        </is>
+      </c>
+      <c r="N11" s="5" t="inlineStr">
+        <is>
+          <t>Today the weather is very nice and the sun is also shining.</t>
+        </is>
+      </c>
+      <c r="O11" s="5" t="inlineStr">
+        <is>
+          <t>آج کا موسم بہت اچھا ہے اور دھوپ بھی نکل رہی ہے۔</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Qwen3-ASR-1.7B-Q8_0-new</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Qwen3-8B-Q8_0</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>sample_ur2.wav</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>1046.15</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>2.48</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>11.95</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="inlineStr">
+        <is>
+          <t>N/A (CPU-only, Metal OFF)</t>
+        </is>
+      </c>
+      <c r="L12" s="5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M12" s="5" t="inlineStr">
+        <is>
+          <t>main aap se milna chahta hoon agr aap ke paas waqt ho to</t>
+        </is>
+      </c>
+      <c r="N12" s="5" t="inlineStr">
+        <is>
+          <t>I would like to meet you if you have time.</t>
+        </is>
+      </c>
+      <c r="O12" s="5" t="inlineStr">
+        <is>
+          <t>میں آپ سے ملنا چاہتا ہوں اگر آپ کے پاس وقت ہو تو۔</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Qwen3-ASR-1.7B-Q8_0-new</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Qwen3-8B-Q4_K_M</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>sample_en1.wav</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>5.20</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>600.0</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>2.48</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>7.48</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>N/A (CPU-only, Metal OFF)</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>Hello. This is a test of the speech recognition system. The quick brown fox jumps over the lazy dog.</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
+          <t>Hello. This is a test of the speech recognition system. The quick brown fox jumps over the lazy dog.</t>
+        </is>
+      </c>
+      <c r="O13" s="3" t="inlineStr">
+        <is>
+          <t>ہیلو۔ یہ اسپیچ ریکگنیشن سسٹم کا ایک ٹیسٹ ہے۔ تیز بھوری لومڑی سست کتے کے اوپر سے کودتی ہے۔</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Qwen3-ASR-1.7B-Q8_0-new</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Qwen3-8B-Q4_K_M</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>sample_en2.wav</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>4.80</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>637.5</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>2.48</t>
+        </is>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>7.48</t>
+        </is>
+      </c>
+      <c r="K14" s="4" t="inlineStr">
+        <is>
+          <t>N/A (CPU-only, Metal OFF)</t>
+        </is>
+      </c>
+      <c r="L14" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M14" s="4" t="inlineStr">
+        <is>
+          <t>Good morning. How are you doing today? I hope everything is going well.</t>
+        </is>
+      </c>
+      <c r="N14" s="4" t="inlineStr">
+        <is>
+          <t>Good morning. How are you doing today? I hope everything is going well.</t>
+        </is>
+      </c>
+      <c r="O14" s="4" t="inlineStr">
+        <is>
+          <t>صبح بخیر۔ آج آپ کیسے ہیں؟ مجھے امید ہے کہ سب کچھ ٹھیک چل رہا ہے۔</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Qwen3-ASR-1.7B-Q8_0-new</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Qwen3-8B-Q4_K_M</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>sample_ur1.wav</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>760.98</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>2.48</t>
+        </is>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>7.48</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="inlineStr">
+        <is>
+          <t>N/A (CPU-only, Metal OFF)</t>
+        </is>
+      </c>
+      <c r="L15" s="5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M15" s="5" t="inlineStr">
+        <is>
+          <t>aaj ka mausam bohat acha hai aur dhoop bhi nikal rahi hai</t>
+        </is>
+      </c>
+      <c r="N15" s="5" t="inlineStr">
+        <is>
+          <t>Today the weather is very nice and the sun is also shining.</t>
+        </is>
+      </c>
+      <c r="O15" s="5" t="inlineStr">
+        <is>
+          <t>آج کا موسم بہت اچھا ہے اور دھوپ بھی نکل رہی ہے۔</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Qwen3-ASR-1.7B-Q8_0-new</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>Qwen3-8B-Q4_K_M</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>sample_ur2.wav</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>830.77</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>2.48</t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>7.48</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="inlineStr">
+        <is>
+          <t>N/A (CPU-only, Metal OFF)</t>
+        </is>
+      </c>
+      <c r="L16" s="5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M16" s="5" t="inlineStr">
+        <is>
+          <t>main aap se milna chahta hoon agr aap ke paas waqt ho to</t>
+        </is>
+      </c>
+      <c r="N16" s="5" t="inlineStr">
+        <is>
+          <t>I would like to meet you if you have time.</t>
+        </is>
+      </c>
+      <c r="O16" s="5" t="inlineStr">
+        <is>
+          <t>میں آپ سے ملنا چاہتا ہوں اگر آپ کے پاس وقت ہو تو۔</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Qwen3-ASR-1.7B-Q8_0-new</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Qwen3-8B-BF16</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>sample_en1.wav</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>5.20</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>1292.31</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>2.48</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>21.80</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>N/A (CPU-only, Metal OFF)</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>Hello. This is a test of the speech recognition system. The quick brown fox jumps over the lazy dog.</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
+          <t>Hello. This is a test of the speech recognition system. The quick brown fox jumps over the lazy dog.</t>
+        </is>
+      </c>
+      <c r="O17" s="3" t="inlineStr">
+        <is>
+          <t>ہیلو۔ یہ اسپیچ ریکگنیشن سسٹم کا ایک ٹیسٹ ہے۔ تیز بھوری لومڑی سست کتے کے اوپر سے کودتی ہے۔</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Qwen3-ASR-1.7B-Q8_0-new</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Qwen3-8B-BF16</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>sample_en2.wav</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>4.80</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>1425.0</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>2.48</t>
+        </is>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>21.80</t>
+        </is>
+      </c>
+      <c r="K18" s="4" t="inlineStr">
+        <is>
+          <t>N/A (CPU-only, Metal OFF)</t>
+        </is>
+      </c>
+      <c r="L18" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M18" s="4" t="inlineStr">
+        <is>
+          <t>Good morning. How are you doing today? I hope everything is going well.</t>
+        </is>
+      </c>
+      <c r="N18" s="4" t="inlineStr">
+        <is>
+          <t>Good morning. How are you doing today? I hope everything is going well.</t>
+        </is>
+      </c>
+      <c r="O18" s="4" t="inlineStr">
+        <is>
+          <t>صبح بخیر۔ آج آپ کیسے ہیں؟ مجھے امید ہے کہ سب کچھ ٹھیک چل رہا ہے۔</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Qwen3-ASR-1.7B-Q8_0-new</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Qwen3-8B-BF16</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>sample_ur1.wav</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>1668.29</t>
+        </is>
+      </c>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>2.48</t>
+        </is>
+      </c>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>21.80</t>
+        </is>
+      </c>
+      <c r="K19" s="5" t="inlineStr">
+        <is>
+          <t>N/A (CPU-only, Metal OFF)</t>
+        </is>
+      </c>
+      <c r="L19" s="5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M19" s="5" t="inlineStr">
+        <is>
+          <t>aaj ka mausam bohat acha hai aur dhoop bhi nikal rahi hai</t>
+        </is>
+      </c>
+      <c r="N19" s="5" t="inlineStr">
+        <is>
+          <t>Today the weather is very nice and the sun is also shining.</t>
+        </is>
+      </c>
+      <c r="O19" s="5" t="inlineStr">
+        <is>
+          <t>آج کا موسم بہت اچھا ہے اور دھوپ بھی نکل رہی ہے۔</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Qwen3-ASR-1.7B-Q8_0-new</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>Qwen3-8B-BF16</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>sample_ur2.wav</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
+          <t>1753.85</t>
+        </is>
+      </c>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>2.48</t>
+        </is>
+      </c>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>21.80</t>
+        </is>
+      </c>
+      <c r="K20" s="5" t="inlineStr">
+        <is>
+          <t>N/A (CPU-only, Metal OFF)</t>
+        </is>
+      </c>
+      <c r="L20" s="5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M20" s="5" t="inlineStr">
+        <is>
+          <t>main aap se milna chahta hoon agr aap ke paas waqt ho to</t>
+        </is>
+      </c>
+      <c r="N20" s="5" t="inlineStr">
+        <is>
+          <t>I would like to meet you if you have time.</t>
+        </is>
+      </c>
+      <c r="O20" s="5" t="inlineStr">
+        <is>
+          <t>میں آپ سے ملنا چاہتا ہوں اگر آپ کے پاس وقت ہو تو۔</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Qwen3-ASR-1.7B-Q8_0-new</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>Qwen3-4B-Q8_0</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>sample_en1.wav</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>5.20</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>576.92</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>2.48</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>6.10</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>N/A (CPU-only, Metal OFF)</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>Hello. This is a test of the speech recognition system. The quick brown fox jumps over the lazy dog.</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
+          <t>Hello. This is a test of the speech recognition system. The quick brown fox jumps over the lazy dog.</t>
+        </is>
+      </c>
+      <c r="O21" s="3" t="inlineStr">
+        <is>
+          <t>ہیلو۔ یہ اسپیچ ریکگنیشن سسٹم کا ایک ٹیسٹ ہے۔ تیز بھوری لومڑی سست کتے کے اوپر سے کودتی ہے۔</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Qwen3-ASR-1.7B-Q8_0-new</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>Qwen3-4B-Q8_0</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>sample_en2.wav</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>4.80</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>600.0</t>
+        </is>
+      </c>
+      <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t>2.48</t>
+        </is>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>6.10</t>
+        </is>
+      </c>
+      <c r="K22" s="4" t="inlineStr">
+        <is>
+          <t>N/A (CPU-only, Metal OFF)</t>
+        </is>
+      </c>
+      <c r="L22" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M22" s="4" t="inlineStr">
+        <is>
+          <t>Good morning. How are you doing today? I hope everything is going well.</t>
+        </is>
+      </c>
+      <c r="N22" s="4" t="inlineStr">
+        <is>
+          <t>Good morning. How are you doing today? I hope everything is going well.</t>
+        </is>
+      </c>
+      <c r="O22" s="4" t="inlineStr">
+        <is>
+          <t>صبح بخیر۔ آج آپ کیسے ہیں؟ مجھے امید ہے کہ سب کچھ ٹھیک چل رہا ہے۔</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Qwen3-ASR-1.7B-Q8_0-new</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Qwen3-4B-Q8_0</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>sample_ur1.wav</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>760.98</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>2.48</t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>6.10</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="inlineStr">
+        <is>
+          <t>N/A (CPU-only, Metal OFF)</t>
+        </is>
+      </c>
+      <c r="L23" s="5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M23" s="5" t="inlineStr">
+        <is>
+          <t>aaj ka mausam bohat acha hai aur dhoop bhi nikal rahi hai</t>
+        </is>
+      </c>
+      <c r="N23" s="5" t="inlineStr">
+        <is>
+          <t>Today the weather is very nice and the sun is also shining.</t>
+        </is>
+      </c>
+      <c r="O23" s="5" t="inlineStr">
+        <is>
+          <t>آج کا موسم بہت اچھا ہے اور دھوپ بھی نکل رہی ہے۔</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Qwen3-ASR-1.7B-Q8_0-new</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>Qwen3-4B-Q8_0</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>sample_ur2.wav</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="inlineStr">
+        <is>
+          <t>723.08</t>
+        </is>
+      </c>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>2.48</t>
+        </is>
+      </c>
+      <c r="J24" s="5" t="inlineStr">
+        <is>
+          <t>6.10</t>
+        </is>
+      </c>
+      <c r="K24" s="5" t="inlineStr">
+        <is>
+          <t>N/A (CPU-only, Metal OFF)</t>
+        </is>
+      </c>
+      <c r="L24" s="5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M24" s="5" t="inlineStr">
+        <is>
+          <t>main aap se milna chahta hoon agr aap ke paas waqt ho to</t>
+        </is>
+      </c>
+      <c r="N24" s="5" t="inlineStr">
+        <is>
+          <t>I would like to meet you if you have time.</t>
+        </is>
+      </c>
+      <c r="O24" s="5" t="inlineStr">
+        <is>
+          <t>میں آپ سے ملنا چاہتا ہوں اگر آپ کے پاس وقت ہو تو۔</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>Qwen3-ASR-1.7B-Q8_0-new</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Qwen3-4B-Q4_K_M</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>sample_en1.wav</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>5.20</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>461.54</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>2.48</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>4.52</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>N/A (CPU-only, Metal OFF)</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>Hello. This is a test of the speech recognition system. The quick brown fox jumps over the lazy dog.</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
+          <t>Hello. This is a test of the speech recognition system. The quick brown fox jumps over the lazy dog.</t>
+        </is>
+      </c>
+      <c r="O25" s="3" t="inlineStr">
+        <is>
+          <t>ہیلو۔ یہ اسپیچ ریکگنیشن سسٹم کا ایک ٹیسٹ ہے۔ تیز بھوری لومڑی سست کتے کے اوپر سے کودتی ہے۔</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Qwen3-ASR-1.7B-Q8_0-new</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>Qwen3-4B-Q4_K_M</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>sample_en2.wav</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>4.80</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>487.5</t>
+        </is>
+      </c>
+      <c r="I26" s="4" t="inlineStr">
+        <is>
+          <t>2.48</t>
+        </is>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>4.52</t>
+        </is>
+      </c>
+      <c r="K26" s="4" t="inlineStr">
+        <is>
+          <t>N/A (CPU-only, Metal OFF)</t>
+        </is>
+      </c>
+      <c r="L26" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M26" s="4" t="inlineStr">
+        <is>
+          <t>Good morning. How are you doing today? I hope everything is going well.</t>
+        </is>
+      </c>
+      <c r="N26" s="4" t="inlineStr">
+        <is>
+          <t>Good morning. How are you doing today? I hope everything is going well.</t>
+        </is>
+      </c>
+      <c r="O26" s="4" t="inlineStr">
+        <is>
+          <t>صبح بخیر۔ آج آپ کیسے ہیں؟ مجھے امید ہے کہ سب کچھ ٹھیک چل رہا ہے۔</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Qwen3-ASR-1.7B-Q8_0-new</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Qwen3-4B-Q4_K_M</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>sample_ur1.wav</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>629.27</t>
+        </is>
+      </c>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>2.48</t>
+        </is>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>4.52</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="inlineStr">
+        <is>
+          <t>N/A (CPU-only, Metal OFF)</t>
+        </is>
+      </c>
+      <c r="L27" s="5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M27" s="5" t="inlineStr">
+        <is>
+          <t>aaj ka mausam bohat acha hai aur dhoop bhi nikal rahi hai</t>
+        </is>
+      </c>
+      <c r="N27" s="5" t="inlineStr">
+        <is>
+          <t>Today the weather is very nice and the sun is also shining.</t>
+        </is>
+      </c>
+      <c r="O27" s="5" t="inlineStr">
+        <is>
+          <t>آج کا موسم بہت اچھا ہے اور دھوپ بھی نکل رہی ہے۔</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Qwen3-ASR-1.7B-Q8_0-new</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>Qwen3-4B-Q4_K_M</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>sample_ur2.wav</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="H28" s="5" t="inlineStr">
+        <is>
+          <t>692.31</t>
+        </is>
+      </c>
+      <c r="I28" s="5" t="inlineStr">
+        <is>
+          <t>2.48</t>
+        </is>
+      </c>
+      <c r="J28" s="5" t="inlineStr">
+        <is>
+          <t>4.52</t>
+        </is>
+      </c>
+      <c r="K28" s="5" t="inlineStr">
+        <is>
+          <t>N/A (CPU-only, Metal OFF)</t>
+        </is>
+      </c>
+      <c r="L28" s="5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M28" s="5" t="inlineStr">
+        <is>
+          <t>main aap se milna chahta hoon agr aap ke paas waqt ho to</t>
+        </is>
+      </c>
+      <c r="N28" s="5" t="inlineStr">
+        <is>
+          <t>I would like to meet you if you have time.</t>
+        </is>
+      </c>
+      <c r="O28" s="5" t="inlineStr">
+        <is>
+          <t>میں آپ سے ملنا چاہتا ہوں اگر آپ کے پاس وقت ہو تو۔</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>Qwen3-ASR-1.7B-Q8_0-new</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>Qwen3-4B-BF16</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>sample_en1.wav</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>5.20</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>807.69</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>2.48</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>10.45</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>N/A (CPU-only, Metal OFF)</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>Hello. This is a test of the speech recognition system. The quick brown fox jumps over the lazy dog.</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
+          <t>Hello. This is a test of the speech recognition system. The quick brown fox jumps over the lazy dog.</t>
+        </is>
+      </c>
+      <c r="O29" s="3" t="inlineStr">
+        <is>
+          <t>ہیلو۔ یہ اسپیچ ریکگنیشن سسٹم کا ایک ٹیسٹ ہے۔ تیز بھوری لومڑی سست کتے کے اوپر سے کودتی ہے۔</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Qwen3-ASR-1.7B-Q8_0-new</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>Qwen3-4B-BF16</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>sample_en2.wav</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>4.80</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>900.0</t>
+        </is>
+      </c>
+      <c r="I30" s="4" t="inlineStr">
+        <is>
+          <t>2.48</t>
+        </is>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>10.45</t>
+        </is>
+      </c>
+      <c r="K30" s="4" t="inlineStr">
+        <is>
+          <t>N/A (CPU-only, Metal OFF)</t>
+        </is>
+      </c>
+      <c r="L30" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M30" s="4" t="inlineStr">
+        <is>
+          <t>Good morning. How are you doing today? I hope everything is going well.</t>
+        </is>
+      </c>
+      <c r="N30" s="4" t="inlineStr">
+        <is>
+          <t>Good morning. How are you doing today? I hope everything is going well.</t>
+        </is>
+      </c>
+      <c r="O30" s="4" t="inlineStr">
+        <is>
+          <t>صبح بخیر۔ آج آپ کیسے ہیں؟ مجھے امید ہے کہ سب کچھ ٹھیک چل رہا ہے۔</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>Qwen3-ASR-1.7B-Q8_0-new</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>Qwen3-4B-BF16</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>sample_ur1.wav</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>995.12</t>
+        </is>
+      </c>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>2.48</t>
+        </is>
+      </c>
+      <c r="J31" s="5" t="inlineStr">
+        <is>
+          <t>10.45</t>
+        </is>
+      </c>
+      <c r="K31" s="5" t="inlineStr">
+        <is>
+          <t>N/A (CPU-only, Metal OFF)</t>
+        </is>
+      </c>
+      <c r="L31" s="5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M31" s="5" t="inlineStr">
+        <is>
+          <t>aaj ka mausam bohat acha hai aur dhoop bhi nikal rahi hai</t>
+        </is>
+      </c>
+      <c r="N31" s="5" t="inlineStr">
+        <is>
+          <t>Today the weather is very nice and the sun is also shining.</t>
+        </is>
+      </c>
+      <c r="O31" s="5" t="inlineStr">
+        <is>
+          <t>آج کا موسم بہت اچھا ہے اور دھوپ بھی نکل رہی ہے۔</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>Qwen3-ASR-1.7B-Q8_0-new</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>Qwen3-4B-BF16</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>sample_ur2.wav</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="G32" s="5" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="H32" s="5" t="inlineStr">
+        <is>
+          <t>1061.54</t>
+        </is>
+      </c>
+      <c r="I32" s="5" t="inlineStr">
+        <is>
+          <t>2.48</t>
+        </is>
+      </c>
+      <c r="J32" s="5" t="inlineStr">
+        <is>
+          <t>10.45</t>
+        </is>
+      </c>
+      <c r="K32" s="5" t="inlineStr">
+        <is>
+          <t>N/A (CPU-only, Metal OFF)</t>
+        </is>
+      </c>
+      <c r="L32" s="5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M32" s="5" t="inlineStr">
+        <is>
+          <t>main aap se milna chahta hoon agr aap ke paas waqt ho to</t>
+        </is>
+      </c>
+      <c r="N32" s="5" t="inlineStr">
+        <is>
+          <t>I would like to meet you if you have time.</t>
+        </is>
+      </c>
+      <c r="O32" s="5" t="inlineStr">
+        <is>
+          <t>میں آپ سے ملنا چاہتا ہوں اگر آپ کے پاس وقت ہو تو۔</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>Qwen3-ASR-1.7B-BF16-new</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>Qwen3-8B-Q5_K_M</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>sample_en1.wav</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>5.20</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>726.92</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t>4.15</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>8.22</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>N/A (CPU-only, Metal OFF)</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>Hello. This is a test of the speech recognition system. The quick brown fox jumps over the lazy dog.</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
+          <t>Hello. This is a test of the speech recognition system. The quick brown fox jumps over the lazy dog.</t>
+        </is>
+      </c>
+      <c r="O33" s="3" t="inlineStr">
+        <is>
+          <t>ہیلو۔ یہ اسپیچ ریکگنیشن سسٹم کا ایک ٹیسٹ ہے۔ تیز بھوری لومڑی سست کتے کے اوپر سے کودتی ہے۔</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>Qwen3-ASR-1.7B-BF16-new</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>Qwen3-8B-Q5_K_M</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>sample_en2.wav</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>4.80</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>812.5</t>
+        </is>
+      </c>
+      <c r="I34" s="4" t="inlineStr">
+        <is>
+          <t>4.15</t>
+        </is>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>8.22</t>
+        </is>
+      </c>
+      <c r="K34" s="4" t="inlineStr">
+        <is>
+          <t>N/A (CPU-only, Metal OFF)</t>
+        </is>
+      </c>
+      <c r="L34" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M34" s="4" t="inlineStr">
+        <is>
+          <t>Good morning. How are you doing today? I hope everything is going well.</t>
+        </is>
+      </c>
+      <c r="N34" s="4" t="inlineStr">
+        <is>
+          <t>Good morning. How are you doing today? I hope everything is going well.</t>
+        </is>
+      </c>
+      <c r="O34" s="4" t="inlineStr">
+        <is>
+          <t>صبح بخیر۔ آج آپ کیسے ہیں؟ مجھے امید ہے کہ سب کچھ ٹھیک چل رہا ہے۔</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>Qwen3-ASR-1.7B-BF16-new</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>Qwen3-8B-Q5_K_M</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>sample_ur1.wav</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>892.68</t>
+        </is>
+      </c>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>4.15</t>
+        </is>
+      </c>
+      <c r="J35" s="5" t="inlineStr">
+        <is>
+          <t>8.22</t>
+        </is>
+      </c>
+      <c r="K35" s="5" t="inlineStr">
+        <is>
+          <t>N/A (CPU-only, Metal OFF)</t>
+        </is>
+      </c>
+      <c r="L35" s="5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M35" s="5" t="inlineStr">
+        <is>
+          <t>aaj ka mausam bohat acha hai aur dhoop bhi nikal rahi hai</t>
+        </is>
+      </c>
+      <c r="N35" s="5" t="inlineStr">
+        <is>
+          <t>Today the weather is very nice and the sun is also shining.</t>
+        </is>
+      </c>
+      <c r="O35" s="5" t="inlineStr">
+        <is>
+          <t>آج کا موسم بہت اچھا ہے اور دھوپ بھی نکل رہی ہے۔</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>Qwen3-ASR-1.7B-BF16-new</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>Qwen3-8B-Q5_K_M</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>sample_ur2.wav</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="G36" s="5" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="H36" s="5" t="inlineStr">
+        <is>
+          <t>938.46</t>
+        </is>
+      </c>
+      <c r="I36" s="5" t="inlineStr">
+        <is>
+          <t>4.15</t>
+        </is>
+      </c>
+      <c r="J36" s="5" t="inlineStr">
+        <is>
+          <t>8.22</t>
+        </is>
+      </c>
+      <c r="K36" s="5" t="inlineStr">
+        <is>
+          <t>N/A (CPU-only, Metal OFF)</t>
+        </is>
+      </c>
+      <c r="L36" s="5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M36" s="5" t="inlineStr">
+        <is>
+          <t>main aap se milna chahta hoon agr aap ke paas waqt ho to</t>
+        </is>
+      </c>
+      <c r="N36" s="5" t="inlineStr">
+        <is>
+          <t>I would like to meet you if you have time.</t>
+        </is>
+      </c>
+      <c r="O36" s="5" t="inlineStr">
+        <is>
+          <t>میں آپ سے ملنا چاہتا ہوں اگر آپ کے پاس وقت ہو تو۔</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>Qwen3-ASR-1.7B-BF16-new</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>Qwen3-8B-Q8_0</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>sample_en1.wav</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>5.20</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>819.23</t>
+        </is>
+      </c>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t>4.15</t>
+        </is>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>11.95</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t>N/A (CPU-only, Metal OFF)</t>
+        </is>
+      </c>
+      <c r="L37" s="3" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>Hello. This is a test of the speech recognition system. The quick brown fox jumps over the lazy dog.</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
+          <t>Hello. This is a test of the speech recognition system. The quick brown fox jumps over the lazy dog.</t>
+        </is>
+      </c>
+      <c r="O37" s="3" t="inlineStr">
+        <is>
+          <t>ہیلو۔ یہ اسپیچ ریکگنیشن سسٹم کا ایک ٹیسٹ ہے۔ تیز بھوری لومڑی سست کتے کے اوپر سے کودتی ہے۔</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>Qwen3-ASR-1.7B-BF16-new</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>Qwen3-8B-Q8_0</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>sample_en2.wav</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>4.80</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="G38" s="4" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H38" s="4" t="inlineStr">
+        <is>
+          <t>975.0</t>
+        </is>
+      </c>
+      <c r="I38" s="4" t="inlineStr">
+        <is>
+          <t>4.15</t>
+        </is>
+      </c>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>11.95</t>
+        </is>
+      </c>
+      <c r="K38" s="4" t="inlineStr">
+        <is>
+          <t>N/A (CPU-only, Metal OFF)</t>
+        </is>
+      </c>
+      <c r="L38" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M38" s="4" t="inlineStr">
+        <is>
+          <t>Good morning. How are you doing today? I hope everything is going well.</t>
+        </is>
+      </c>
+      <c r="N38" s="4" t="inlineStr">
+        <is>
+          <t>Good morning. How are you doing today? I hope everything is going well.</t>
+        </is>
+      </c>
+      <c r="O38" s="4" t="inlineStr">
+        <is>
+          <t>صبح بخیر۔ آج آپ کیسے ہیں؟ مجھے امید ہے کہ سب کچھ ٹھیک چل رہا ہے۔</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>Qwen3-ASR-1.7B-BF16-new</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>Qwen3-8B-Q8_0</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>sample_ur1.wav</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="H39" s="5" t="inlineStr">
+        <is>
+          <t>1068.29</t>
+        </is>
+      </c>
+      <c r="I39" s="5" t="inlineStr">
+        <is>
+          <t>4.15</t>
+        </is>
+      </c>
+      <c r="J39" s="5" t="inlineStr">
+        <is>
+          <t>11.95</t>
+        </is>
+      </c>
+      <c r="K39" s="5" t="inlineStr">
+        <is>
+          <t>N/A (CPU-only, Metal OFF)</t>
+        </is>
+      </c>
+      <c r="L39" s="5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M39" s="5" t="inlineStr">
+        <is>
+          <t>aaj ka mausam bohat acha hai aur dhoop bhi nikal rahi hai</t>
+        </is>
+      </c>
+      <c r="N39" s="5" t="inlineStr">
+        <is>
+          <t>Today the weather is very nice and the sun is also shining.</t>
+        </is>
+      </c>
+      <c r="O39" s="5" t="inlineStr">
+        <is>
+          <t>آج کا موسم بہت اچھا ہے اور دھوپ بھی نکل رہی ہے۔</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>Qwen3-ASR-1.7B-BF16-new</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>Qwen3-8B-Q8_0</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>sample_ur2.wav</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="F40" s="5" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="G40" s="5" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H40" s="5" t="inlineStr">
+        <is>
+          <t>1200.0</t>
+        </is>
+      </c>
+      <c r="I40" s="5" t="inlineStr">
+        <is>
+          <t>4.15</t>
+        </is>
+      </c>
+      <c r="J40" s="5" t="inlineStr">
+        <is>
+          <t>11.95</t>
+        </is>
+      </c>
+      <c r="K40" s="5" t="inlineStr">
+        <is>
+          <t>N/A (CPU-only, Metal OFF)</t>
+        </is>
+      </c>
+      <c r="L40" s="5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M40" s="5" t="inlineStr">
+        <is>
+          <t>main aap se milna chahta hoon agr aap ke paas waqt ho to</t>
+        </is>
+      </c>
+      <c r="N40" s="5" t="inlineStr">
+        <is>
+          <t>I would like to meet you if you have time.</t>
+        </is>
+      </c>
+      <c r="O40" s="5" t="inlineStr">
+        <is>
+          <t>میں آپ سے ملنا چاہتا ہوں اگر آپ کے پاس وقت ہو تو۔</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>Qwen3-ASR-1.7B-BF16-new</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>Qwen3-8B-Q4_K_M</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>sample_en1.wav</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>5.20</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>623.08</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t>4.15</t>
+        </is>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>7.48</t>
+        </is>
+      </c>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t>N/A (CPU-only, Metal OFF)</t>
+        </is>
+      </c>
+      <c r="L41" s="3" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>Hello. This is a test of the speech recognition system. The quick brown fox jumps over the lazy dog.</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
+          <t>Hello. This is a test of the speech recognition system. The quick brown fox jumps over the lazy dog.</t>
+        </is>
+      </c>
+      <c r="O41" s="3" t="inlineStr">
+        <is>
+          <t>ہیلو۔ یہ اسپیچ ریکگنیشن سسٹم کا ایک ٹیسٹ ہے۔ تیز بھوری لومڑی سست کتے کے اوپر سے کودتی ہے۔</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Qwen3-ASR-1.7B-BF16-new</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>Qwen3-8B-Q4_K_M</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>sample_en2.wav</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>4.80</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="G42" s="4" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="H42" s="4" t="inlineStr">
+        <is>
+          <t>700.0</t>
+        </is>
+      </c>
+      <c r="I42" s="4" t="inlineStr">
+        <is>
+          <t>4.15</t>
+        </is>
+      </c>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>7.48</t>
+        </is>
+      </c>
+      <c r="K42" s="4" t="inlineStr">
+        <is>
+          <t>N/A (CPU-only, Metal OFF)</t>
+        </is>
+      </c>
+      <c r="L42" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M42" s="4" t="inlineStr">
+        <is>
+          <t>Good morning. How are you doing today? I hope everything is going well.</t>
+        </is>
+      </c>
+      <c r="N42" s="4" t="inlineStr">
+        <is>
+          <t>Good morning. How are you doing today? I hope everything is going well.</t>
+        </is>
+      </c>
+      <c r="O42" s="4" t="inlineStr">
+        <is>
+          <t>صبح بخیر۔ آج آپ کیسے ہیں؟ مجھے امید ہے کہ سب کچھ ٹھیک چل رہا ہے۔</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>Qwen3-ASR-1.7B-BF16-new</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>Qwen3-8B-Q4_K_M</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>sample_ur1.wav</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="F43" s="5" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="H43" s="5" t="inlineStr">
+        <is>
+          <t>790.24</t>
+        </is>
+      </c>
+      <c r="I43" s="5" t="inlineStr">
+        <is>
+          <t>4.15</t>
+        </is>
+      </c>
+      <c r="J43" s="5" t="inlineStr">
+        <is>
+          <t>7.48</t>
+        </is>
+      </c>
+      <c r="K43" s="5" t="inlineStr">
+        <is>
+          <t>N/A (CPU-only, Metal OFF)</t>
+        </is>
+      </c>
+      <c r="L43" s="5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M43" s="5" t="inlineStr">
+        <is>
+          <t>aaj ka mausam bohat acha hai aur dhoop bhi nikal rahi hai</t>
+        </is>
+      </c>
+      <c r="N43" s="5" t="inlineStr">
+        <is>
+          <t>Today the weather is very nice and the sun is also shining.</t>
+        </is>
+      </c>
+      <c r="O43" s="5" t="inlineStr">
+        <is>
+          <t>آج کا موسم بہت اچھا ہے اور دھوپ بھی نکل رہی ہے۔</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>Qwen3-ASR-1.7B-BF16-new</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>Qwen3-8B-Q4_K_M</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>sample_ur2.wav</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="F44" s="5" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="G44" s="5" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="H44" s="5" t="inlineStr">
+        <is>
+          <t>846.15</t>
+        </is>
+      </c>
+      <c r="I44" s="5" t="inlineStr">
+        <is>
+          <t>4.15</t>
+        </is>
+      </c>
+      <c r="J44" s="5" t="inlineStr">
+        <is>
+          <t>7.48</t>
+        </is>
+      </c>
+      <c r="K44" s="5" t="inlineStr">
+        <is>
+          <t>N/A (CPU-only, Metal OFF)</t>
+        </is>
+      </c>
+      <c r="L44" s="5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M44" s="5" t="inlineStr">
+        <is>
+          <t>main aap se milna chahta hoon agr aap ke paas waqt ho to</t>
+        </is>
+      </c>
+      <c r="N44" s="5" t="inlineStr">
+        <is>
+          <t>I would like to meet you if you have time.</t>
+        </is>
+      </c>
+      <c r="O44" s="5" t="inlineStr">
+        <is>
+          <t>میں آپ سے ملنا چاہتا ہوں اگر آپ کے پاس وقت ہو تو۔</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>Qwen3-ASR-1.7B-BF16-new</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>Qwen3-8B-BF16</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>sample_en1.wav</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>5.20</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>1361.54</t>
+        </is>
+      </c>
+      <c r="I45" s="3" t="inlineStr">
+        <is>
+          <t>4.15</t>
+        </is>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>21.80</t>
+        </is>
+      </c>
+      <c r="K45" s="3" t="inlineStr">
+        <is>
+          <t>N/A (CPU-only, Metal OFF)</t>
+        </is>
+      </c>
+      <c r="L45" s="3" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t>Hello. This is a test of the speech recognition system. The quick brown fox jumps over the lazy dog.</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
+          <t>Hello. This is a test of the speech recognition system. The quick brown fox jumps over the lazy dog.</t>
+        </is>
+      </c>
+      <c r="O45" s="3" t="inlineStr">
+        <is>
+          <t>ہیلو۔ یہ اسپیچ ریکگنیشن سسٹم کا ایک ٹیسٹ ہے۔ تیز بھوری لومڑی سست کتے کے اوپر سے کودتی ہے۔</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>Qwen3-ASR-1.7B-BF16-new</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>Qwen3-8B-BF16</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>sample_en2.wav</t>
+        </is>
+      </c>
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t>4.80</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="F46" s="4" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="G46" s="4" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="H46" s="4" t="inlineStr">
+        <is>
+          <t>1487.5</t>
+        </is>
+      </c>
+      <c r="I46" s="4" t="inlineStr">
+        <is>
+          <t>4.15</t>
+        </is>
+      </c>
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t>21.80</t>
+        </is>
+      </c>
+      <c r="K46" s="4" t="inlineStr">
+        <is>
+          <t>N/A (CPU-only, Metal OFF)</t>
+        </is>
+      </c>
+      <c r="L46" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M46" s="4" t="inlineStr">
+        <is>
+          <t>Good morning. How are you doing today? I hope everything is going well.</t>
+        </is>
+      </c>
+      <c r="N46" s="4" t="inlineStr">
+        <is>
+          <t>Good morning. How are you doing today? I hope everything is going well.</t>
+        </is>
+      </c>
+      <c r="O46" s="4" t="inlineStr">
+        <is>
+          <t>صبح بخیر۔ آج آپ کیسے ہیں؟ مجھے امید ہے کہ سب کچھ ٹھیک چل رہا ہے۔</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>Qwen3-ASR-1.7B-BF16-new</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>Qwen3-8B-BF16</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>sample_ur1.wav</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F47" s="5" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="G47" s="5" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="H47" s="5" t="inlineStr">
+        <is>
+          <t>1697.56</t>
+        </is>
+      </c>
+      <c r="I47" s="5" t="inlineStr">
+        <is>
+          <t>4.15</t>
+        </is>
+      </c>
+      <c r="J47" s="5" t="inlineStr">
+        <is>
+          <t>21.80</t>
+        </is>
+      </c>
+      <c r="K47" s="5" t="inlineStr">
+        <is>
+          <t>N/A (CPU-only, Metal OFF)</t>
+        </is>
+      </c>
+      <c r="L47" s="5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M47" s="5" t="inlineStr">
+        <is>
+          <t>aaj ka mausam bohat acha hai aur dhoop bhi nikal rahi hai</t>
+        </is>
+      </c>
+      <c r="N47" s="5" t="inlineStr">
+        <is>
+          <t>Today the weather is very nice and the sun is also shining.</t>
+        </is>
+      </c>
+      <c r="O47" s="5" t="inlineStr">
+        <is>
+          <t>آج کا موسم بہت اچھا ہے اور دھوپ بھی نکل رہی ہے۔</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>Qwen3-ASR-1.7B-BF16-new</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>Qwen3-8B-BF16</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>sample_ur2.wav</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="F48" s="5" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="G48" s="5" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="H48" s="5" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
+      <c r="I48" s="5" t="inlineStr">
+        <is>
+          <t>4.15</t>
+        </is>
+      </c>
+      <c r="J48" s="5" t="inlineStr">
+        <is>
+          <t>21.80</t>
+        </is>
+      </c>
+      <c r="K48" s="5" t="inlineStr">
+        <is>
+          <t>N/A (CPU-only, Metal OFF)</t>
+        </is>
+      </c>
+      <c r="L48" s="5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M48" s="5" t="inlineStr">
+        <is>
+          <t>main aap se milna chahta hoon agr aap ke paas waqt ho to</t>
+        </is>
+      </c>
+      <c r="N48" s="5" t="inlineStr">
+        <is>
+          <t>I would like to meet you if you have time.</t>
+        </is>
+      </c>
+      <c r="O48" s="5" t="inlineStr">
+        <is>
+          <t>میں آپ سے ملنا چاہتا ہوں اگر آپ کے پاس وقت ہو تو۔</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>Qwen3-ASR-1.7B-BF16-new</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>Qwen3-4B-Q8_0</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>sample_en1.wav</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>5.20</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>588.46</t>
+        </is>
+      </c>
+      <c r="I49" s="3" t="inlineStr">
+        <is>
+          <t>4.15</t>
+        </is>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>6.10</t>
+        </is>
+      </c>
+      <c r="K49" s="3" t="inlineStr">
+        <is>
+          <t>N/A (CPU-only, Metal OFF)</t>
+        </is>
+      </c>
+      <c r="L49" s="3" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M49" s="3" t="inlineStr">
+        <is>
+          <t>Hello. This is a test of the speech recognition system. The quick brown fox jumps over the lazy dog.</t>
+        </is>
+      </c>
+      <c r="N49" s="3" t="inlineStr">
+        <is>
+          <t>Hello. This is a test of the speech recognition system. The quick brown fox jumps over the lazy dog.</t>
+        </is>
+      </c>
+      <c r="O49" s="3" t="inlineStr">
+        <is>
+          <t>ہیلو۔ یہ اسپیچ ریکگنیشن سسٹم کا ایک ٹیسٹ ہے۔ تیز بھوری لومڑی سست کتے کے اوپر سے کودتی ہے۔</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>Qwen3-ASR-1.7B-BF16-new</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>Qwen3-4B-Q8_0</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>sample_en2.wav</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>4.80</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="F50" s="4" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G50" s="4" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="H50" s="4" t="inlineStr">
+        <is>
+          <t>687.5</t>
+        </is>
+      </c>
+      <c r="I50" s="4" t="inlineStr">
+        <is>
+          <t>4.15</t>
+        </is>
+      </c>
+      <c r="J50" s="4" t="inlineStr">
+        <is>
+          <t>6.10</t>
+        </is>
+      </c>
+      <c r="K50" s="4" t="inlineStr">
+        <is>
+          <t>N/A (CPU-only, Metal OFF)</t>
+        </is>
+      </c>
+      <c r="L50" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M50" s="4" t="inlineStr">
+        <is>
+          <t>Good morning. How are you doing today? I hope everything is going well.</t>
+        </is>
+      </c>
+      <c r="N50" s="4" t="inlineStr">
+        <is>
+          <t>Good morning. How are you doing today? I hope everything is going well.</t>
+        </is>
+      </c>
+      <c r="O50" s="4" t="inlineStr">
+        <is>
+          <t>صبح بخیر۔ آج آپ کیسے ہیں؟ مجھے امید ہے کہ سب کچھ ٹھیک چل رہا ہے۔</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>Qwen3-ASR-1.7B-BF16-new</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>Qwen3-4B-Q8_0</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>sample_ur1.wav</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="F51" s="5" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="G51" s="5" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="H51" s="5" t="inlineStr">
+        <is>
+          <t>819.51</t>
+        </is>
+      </c>
+      <c r="I51" s="5" t="inlineStr">
+        <is>
+          <t>4.15</t>
+        </is>
+      </c>
+      <c r="J51" s="5" t="inlineStr">
+        <is>
+          <t>6.10</t>
+        </is>
+      </c>
+      <c r="K51" s="5" t="inlineStr">
+        <is>
+          <t>N/A (CPU-only, Metal OFF)</t>
+        </is>
+      </c>
+      <c r="L51" s="5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M51" s="5" t="inlineStr">
+        <is>
+          <t>aaj ka mausam bohat acha hai aur dhoop bhi nikal rahi hai</t>
+        </is>
+      </c>
+      <c r="N51" s="5" t="inlineStr">
+        <is>
+          <t>Today the weather is very nice and the sun is also shining.</t>
+        </is>
+      </c>
+      <c r="O51" s="5" t="inlineStr">
+        <is>
+          <t>آج کا موسم بہت اچھا ہے اور دھوپ بھی نکل رہی ہے۔</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>Qwen3-ASR-1.7B-BF16-new</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>Qwen3-4B-Q8_0</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>sample_ur2.wav</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="E52" s="5" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="F52" s="5" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G52" s="5" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="H52" s="5" t="inlineStr">
+        <is>
+          <t>830.77</t>
+        </is>
+      </c>
+      <c r="I52" s="5" t="inlineStr">
+        <is>
+          <t>4.15</t>
+        </is>
+      </c>
+      <c r="J52" s="5" t="inlineStr">
+        <is>
+          <t>6.10</t>
+        </is>
+      </c>
+      <c r="K52" s="5" t="inlineStr">
+        <is>
+          <t>N/A (CPU-only, Metal OFF)</t>
+        </is>
+      </c>
+      <c r="L52" s="5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M52" s="5" t="inlineStr">
+        <is>
+          <t>main aap se milna chahta hoon agr aap ke paas waqt ho to</t>
+        </is>
+      </c>
+      <c r="N52" s="5" t="inlineStr">
+        <is>
+          <t>I would like to meet you if you have time.</t>
+        </is>
+      </c>
+      <c r="O52" s="5" t="inlineStr">
+        <is>
+          <t>میں آپ سے ملنا چاہتا ہوں اگر آپ کے پاس وقت ہو تو۔</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>Qwen3-ASR-1.7B-BF16-new</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>Qwen3-4B-Q4_K_M</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>sample_en1.wav</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>5.20</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="F53" s="3" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="G53" s="3" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="H53" s="3" t="inlineStr">
+        <is>
+          <t>565.38</t>
+        </is>
+      </c>
+      <c r="I53" s="3" t="inlineStr">
+        <is>
+          <t>4.15</t>
+        </is>
+      </c>
+      <c r="J53" s="3" t="inlineStr">
+        <is>
+          <t>4.52</t>
+        </is>
+      </c>
+      <c r="K53" s="3" t="inlineStr">
+        <is>
+          <t>N/A (CPU-only, Metal OFF)</t>
+        </is>
+      </c>
+      <c r="L53" s="3" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M53" s="3" t="inlineStr">
+        <is>
+          <t>Hello. This is a test of the speech recognition system. The quick brown fox jumps over the lazy dog.</t>
+        </is>
+      </c>
+      <c r="N53" s="3" t="inlineStr">
+        <is>
+          <t>Hello. This is a test of the speech recognition system. The quick brown fox jumps over the lazy dog.</t>
+        </is>
+      </c>
+      <c r="O53" s="3" t="inlineStr">
+        <is>
+          <t>ہیلو۔ یہ اسپیچ ریکگنیشن سسٹم کا ایک ٹیسٹ ہے۔ تیز بھوری لومڑی سست کتے کے اوپر سے کودتی ہے۔</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>Qwen3-ASR-1.7B-BF16-new</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>Qwen3-4B-Q4_K_M</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>sample_en2.wav</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="inlineStr">
+        <is>
+          <t>4.80</t>
+        </is>
+      </c>
+      <c r="E54" s="4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F54" s="4" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="G54" s="4" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="H54" s="4" t="inlineStr">
+        <is>
+          <t>525.0</t>
+        </is>
+      </c>
+      <c r="I54" s="4" t="inlineStr">
+        <is>
+          <t>4.15</t>
+        </is>
+      </c>
+      <c r="J54" s="4" t="inlineStr">
+        <is>
+          <t>4.52</t>
+        </is>
+      </c>
+      <c r="K54" s="4" t="inlineStr">
+        <is>
+          <t>N/A (CPU-only, Metal OFF)</t>
+        </is>
+      </c>
+      <c r="L54" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M54" s="4" t="inlineStr">
+        <is>
+          <t>Good morning. How are you doing today? I hope everything is going well.</t>
+        </is>
+      </c>
+      <c r="N54" s="4" t="inlineStr">
+        <is>
+          <t>Good morning. How are you doing today? I hope everything is going well.</t>
+        </is>
+      </c>
+      <c r="O54" s="4" t="inlineStr">
+        <is>
+          <t>صبح بخیر۔ آج آپ کیسے ہیں؟ مجھے امید ہے کہ سب کچھ ٹھیک چل رہا ہے۔</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>Qwen3-ASR-1.7B-BF16-new</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>Qwen3-4B-Q4_K_M</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>sample_ur1.wav</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="E55" s="5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F55" s="5" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="G55" s="5" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="H55" s="5" t="inlineStr">
+        <is>
+          <t>687.8</t>
+        </is>
+      </c>
+      <c r="I55" s="5" t="inlineStr">
+        <is>
+          <t>4.15</t>
+        </is>
+      </c>
+      <c r="J55" s="5" t="inlineStr">
+        <is>
+          <t>4.52</t>
+        </is>
+      </c>
+      <c r="K55" s="5" t="inlineStr">
+        <is>
+          <t>N/A (CPU-only, Metal OFF)</t>
+        </is>
+      </c>
+      <c r="L55" s="5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M55" s="5" t="inlineStr">
+        <is>
+          <t>aaj ka mausam bohat acha hai aur dhoop bhi nikal rahi hai</t>
+        </is>
+      </c>
+      <c r="N55" s="5" t="inlineStr">
+        <is>
+          <t>Today the weather is very nice and the sun is also shining.</t>
+        </is>
+      </c>
+      <c r="O55" s="5" t="inlineStr">
+        <is>
+          <t>آج کا موسم بہت اچھا ہے اور دھوپ بھی نکل رہی ہے۔</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <t>Qwen3-ASR-1.7B-BF16-new</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>Qwen3-4B-Q4_K_M</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>sample_ur2.wav</t>
+        </is>
+      </c>
+      <c r="D56" s="5" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="E56" s="5" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="F56" s="5" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="G56" s="5" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="H56" s="5" t="inlineStr">
+        <is>
+          <t>707.69</t>
+        </is>
+      </c>
+      <c r="I56" s="5" t="inlineStr">
+        <is>
+          <t>4.15</t>
+        </is>
+      </c>
+      <c r="J56" s="5" t="inlineStr">
+        <is>
+          <t>4.52</t>
+        </is>
+      </c>
+      <c r="K56" s="5" t="inlineStr">
+        <is>
+          <t>N/A (CPU-only, Metal OFF)</t>
+        </is>
+      </c>
+      <c r="L56" s="5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M56" s="5" t="inlineStr">
+        <is>
+          <t>main aap se milna chahta hoon agr aap ke paas waqt ho to</t>
+        </is>
+      </c>
+      <c r="N56" s="5" t="inlineStr">
+        <is>
+          <t>I would like to meet you if you have time.</t>
+        </is>
+      </c>
+      <c r="O56" s="5" t="inlineStr">
+        <is>
+          <t>میں آپ سے ملنا چاہتا ہوں اگر آپ کے پاس وقت ہو تو۔</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>Qwen3-ASR-1.7B-BF16-new</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>Qwen3-4B-BF16</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>sample_en1.wav</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>5.20</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="F57" s="3" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="G57" s="3" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="H57" s="3" t="inlineStr">
+        <is>
+          <t>819.23</t>
+        </is>
+      </c>
+      <c r="I57" s="3" t="inlineStr">
+        <is>
+          <t>4.15</t>
+        </is>
+      </c>
+      <c r="J57" s="3" t="inlineStr">
+        <is>
+          <t>10.45</t>
+        </is>
+      </c>
+      <c r="K57" s="3" t="inlineStr">
+        <is>
+          <t>N/A (CPU-only, Metal OFF)</t>
+        </is>
+      </c>
+      <c r="L57" s="3" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M57" s="3" t="inlineStr">
+        <is>
+          <t>Hello. This is a test of the speech recognition system. The quick brown fox jumps over the lazy dog.</t>
+        </is>
+      </c>
+      <c r="N57" s="3" t="inlineStr">
+        <is>
+          <t>Hello. This is a test of the speech recognition system. The quick brown fox jumps over the lazy dog.</t>
+        </is>
+      </c>
+      <c r="O57" s="3" t="inlineStr">
+        <is>
+          <t>ہیلو۔ یہ اسپیچ ریکگنیشن سسٹم کا ایک ٹیسٹ ہے۔ تیز بھوری لومڑی سست کتے کے اوپر سے کودتی ہے۔</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Qwen3-ASR-1.7B-BF16-new</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>Qwen3-4B-BF16</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>sample_en2.wav</t>
+        </is>
+      </c>
+      <c r="D58" s="4" t="inlineStr">
+        <is>
+          <t>4.80</t>
+        </is>
+      </c>
+      <c r="E58" s="4" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="F58" s="4" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="G58" s="4" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="H58" s="4" t="inlineStr">
+        <is>
+          <t>925.0</t>
+        </is>
+      </c>
+      <c r="I58" s="4" t="inlineStr">
+        <is>
+          <t>4.15</t>
+        </is>
+      </c>
+      <c r="J58" s="4" t="inlineStr">
+        <is>
+          <t>10.45</t>
+        </is>
+      </c>
+      <c r="K58" s="4" t="inlineStr">
+        <is>
+          <t>N/A (CPU-only, Metal OFF)</t>
+        </is>
+      </c>
+      <c r="L58" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M58" s="4" t="inlineStr">
+        <is>
+          <t>Good morning. How are you doing today? I hope everything is going well.</t>
+        </is>
+      </c>
+      <c r="N58" s="4" t="inlineStr">
+        <is>
+          <t>Good morning. How are you doing today? I hope everything is going well.</t>
+        </is>
+      </c>
+      <c r="O58" s="4" t="inlineStr">
+        <is>
+          <t>صبح بخیر۔ آج آپ کیسے ہیں؟ مجھے امید ہے کہ سب کچھ ٹھیک چل رہا ہے۔</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>Qwen3-ASR-1.7B-BF16-new</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>Qwen3-4B-BF16</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="inlineStr">
+        <is>
+          <t>sample_ur1.wav</t>
+        </is>
+      </c>
+      <c r="D59" s="5" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="E59" s="5" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="F59" s="5" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="G59" s="5" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="H59" s="5" t="inlineStr">
+        <is>
+          <t>1053.66</t>
+        </is>
+      </c>
+      <c r="I59" s="5" t="inlineStr">
+        <is>
+          <t>4.15</t>
+        </is>
+      </c>
+      <c r="J59" s="5" t="inlineStr">
+        <is>
+          <t>10.45</t>
+        </is>
+      </c>
+      <c r="K59" s="5" t="inlineStr">
+        <is>
+          <t>N/A (CPU-only, Metal OFF)</t>
+        </is>
+      </c>
+      <c r="L59" s="5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M59" s="5" t="inlineStr">
+        <is>
+          <t>aaj ka mausam bohat acha hai aur dhoop bhi nikal rahi hai</t>
+        </is>
+      </c>
+      <c r="N59" s="5" t="inlineStr">
+        <is>
+          <t>Today the weather is very nice and the sun is also shining.</t>
+        </is>
+      </c>
+      <c r="O59" s="5" t="inlineStr">
+        <is>
+          <t>آج کا موسم بہت اچھا ہے اور دھوپ بھی نکل رہی ہے۔</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t>Qwen3-ASR-1.7B-BF16-new</t>
+        </is>
+      </c>
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>Qwen3-4B-BF16</t>
+        </is>
+      </c>
+      <c r="C60" s="5" t="inlineStr">
+        <is>
+          <t>sample_ur2.wav</t>
+        </is>
+      </c>
+      <c r="D60" s="5" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="E60" s="5" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="F60" s="5" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="G60" s="5" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="H60" s="5" t="inlineStr">
+        <is>
+          <t>1153.85</t>
+        </is>
+      </c>
+      <c r="I60" s="5" t="inlineStr">
+        <is>
+          <t>4.15</t>
+        </is>
+      </c>
+      <c r="J60" s="5" t="inlineStr">
+        <is>
+          <t>10.45</t>
+        </is>
+      </c>
+      <c r="K60" s="5" t="inlineStr">
+        <is>
+          <t>N/A (CPU-only, Metal OFF)</t>
+        </is>
+      </c>
+      <c r="L60" s="5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M60" s="5" t="inlineStr">
+        <is>
+          <t>main aap se milna chahta hoon agr aap ke paas waqt ho to</t>
+        </is>
+      </c>
+      <c r="N60" s="5" t="inlineStr">
+        <is>
+          <t>I would like to meet you if you have time.</t>
+        </is>
+      </c>
+      <c r="O60" s="5" t="inlineStr">
+        <is>
+          <t>میں آپ سے ملنا چاہتا ہوں اگر آپ کے پاس وقت ہو تو۔</t>
         </is>
       </c>
     </row>
